--- a/marketing_report/outputs/Posgrados/Informe_Analitico/Tablas_Informe_Analitico.xlsx
+++ b/marketing_report/outputs/Posgrados/Informe_Analitico/Tablas_Informe_Analitico.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>133</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>84</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>115</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>84</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>222</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
@@ -715,7 +715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
@@ -786,17 +786,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Origen (4)</t>
+          <t>Chatbot</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
@@ -805,17 +805,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chatbot</t>
+          <t>Origen (4)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
         <v>100</v>
@@ -881,7 +881,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Origen (494)</t>
+          <t>Origen (394)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -900,7 +900,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Origen (701)</t>
+          <t>Origen (494)</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -919,7 +919,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Origen (74)</t>
+          <t>Origen (701)</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -938,19 +938,38 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Origen (74)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Origen (908)</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
         <v>100</v>
       </c>
     </row>

--- a/marketing_report/outputs/Posgrados/Informe_Analitico/Tablas_Informe_Analitico.xlsx
+++ b/marketing_report/outputs/Posgrados/Informe_Analitico/Tablas_Informe_Analitico.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>91</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>221</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="C2" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
@@ -715,7 +715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D2" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
         <v>16</v>
@@ -805,17 +805,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Origen (4)</t>
+          <t>Origen (103)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>100</v>
@@ -824,17 +824,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>Origen (4)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
@@ -843,17 +843,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Origen (103)</t>
+          <t>Desconocido</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>100</v>
@@ -862,7 +862,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Origen (27)</t>
+          <t>Origen (394)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -881,7 +881,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Origen (394)</t>
+          <t>Origen (494)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -900,7 +900,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Origen (494)</t>
+          <t>Origen (701)</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -919,7 +919,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Origen (701)</t>
+          <t>Origen (74)</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -938,7 +938,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Origen (74)</t>
+          <t>Origen (908)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -951,25 +951,6 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Origen (908)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
         <v>100</v>
       </c>
     </row>
